--- a/nebullaone/docs/Vendor_Module_Benchmark_NebullaOne.xlsx
+++ b/nebullaone/docs/Vendor_Module_Benchmark_NebullaOne.xlsx
@@ -9976,7 +9976,7 @@
       </c>
       <c r="G302" s="15" t="inlineStr">
         <is>
-          <t>Receive goods → Quality inspection (Inspected by, verified by — must differ)</t>
+          <t>Receive goods → Quality inspection (Inspected by, verified by)</t>
         </is>
       </c>
       <c r="H302" s="15" t="inlineStr"/>
